--- a/data/11Maj-Gold_Diggers-v-Tigers.xlsx
+++ b/data/11Maj-Gold_Diggers-v-Tigers.xlsx
@@ -325,7 +325,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:O139"/>
   <sheetData>
     <row r="1">
@@ -438,8 +438,10 @@
       <c r="D6" t="s">
         <v>22</v>
       </c>
-      <c r="E6" t="s">
-        <v>23</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>DG</t>
+        </is>
       </c>
       <c r="I6" t="s">
         <v>18</v>
@@ -472,8 +474,10 @@
       <c r="D8" t="s">
         <v>16</v>
       </c>
-      <c r="E8" t="s">
-        <v>26</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>UCDN</t>
+        </is>
       </c>
       <c r="I8" t="s">
         <v>27</v>
@@ -549,8 +553,10 @@
       <c r="D12" t="s">
         <v>16</v>
       </c>
-      <c r="E12" t="s">
-        <v>35</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
       </c>
       <c r="I12" t="s">
         <v>36</v>
@@ -757,8 +763,10 @@
       <c r="D26" t="s">
         <v>22</v>
       </c>
-      <c r="E26" t="s">
-        <v>50</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>DGLG</t>
+        </is>
       </c>
       <c r="I26" t="s">
         <v>36</v>
@@ -847,8 +855,10 @@
       <c r="D35" t="s">
         <v>16</v>
       </c>
-      <c r="E35" t="s">
-        <v>53</v>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>DCSCBC</t>
+        </is>
       </c>
       <c r="I35" t="s">
         <v>18</v>
@@ -962,8 +972,10 @@
       <c r="D43" t="s">
         <v>16</v>
       </c>
-      <c r="E43" t="s">
-        <v>63</v>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>BCFMDN</t>
+        </is>
       </c>
       <c r="I43" t="s">
         <v>18</v>
@@ -1591,8 +1603,10 @@
       <c r="D98" t="s">
         <v>16</v>
       </c>
-      <c r="E98" t="s">
-        <v>87</v>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>UCDC</t>
+        </is>
       </c>
       <c r="I98" t="s">
         <v>27</v>
@@ -1914,8 +1928,10 @@
       <c r="D126" t="s">
         <v>16</v>
       </c>
-      <c r="E126" t="s">
-        <v>95</v>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>DCUCLC</t>
+        </is>
       </c>
       <c r="I126" t="s">
         <v>18</v>
